--- a/results_v3/tables/table1_main_comparison.xlsx
+++ b/results_v3/tables/table1_main_comparison.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,22 +567,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DQN</t>
+          <t>POMCP (known model)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.33±0.05</t>
+          <t>0.91±0.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.67±1.03</t>
+          <t>5.79±0.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.22±0.89</t>
+          <t>7.96±0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -592,34 +592,34 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-13.78±0.94</t>
+          <t>1.34±0.04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15.57±0.46</t>
+          <t>7.06±0.02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PPO</t>
+          <t>DQN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.30±0.03</t>
+          <t>0.33±0.05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11.34±2.27</t>
+          <t>6.67±1.03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.33±1.04</t>
+          <t>22.22±0.89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -629,47 +629,158 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-16.06±1.13</t>
+          <t>-13.78±0.94</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>17.36±0.85</t>
+          <t>15.57±0.46</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PPO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.30±0.03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11.34±2.27</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>24.33±1.04</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.05±0.00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-16.06±1.13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>17.36±0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DQN-GRU (memory)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.45±0.05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9.03±0.80</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20.59±1.06</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.05±0.00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-12.10±1.13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15.07±0.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PPO-Stack (memory)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.34±0.07</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6.64±1.16</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>22.14±1.36</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.05±0.00</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-13.69±1.42</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15.53±0.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>MuZero (ours)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>0.68±0.04</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>8.94±0.81</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>15.68±1.30</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>0.05±0.00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>-6.92±1.39</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>12.46±0.90</t>
         </is>
